--- a/nonprofit_employee_forms/012_donor_transparency_expectation_poll--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/012_donor_transparency_expectation_poll--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Donor Expectations</t>
+          <t>Donor Expectations (2)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>transparency_expectations</t>
+          <t>transparency_expectations_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Transparency Expectations</t>
+          <t>Transparency Expectations 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>accountability_expectations</t>
+          <t>accountability_expectations_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Accountability Expectations</t>
+          <t>Accountability Expectations 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -871,7 +871,7 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -947,7 +947,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>transparency_expectations_choices</t>
+          <t>transparency_expectations_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>transparency_expectations_choices</t>
+          <t>transparency_expectations_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>transparency_expectations_choices</t>
+          <t>transparency_expectations_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>accountability_expectations_choices</t>
+          <t>accountability_expectations_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>accountability_expectations_choices</t>
+          <t>accountability_expectations_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>accountability_expectations_choices</t>
+          <t>accountability_expectations_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
